--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125043766</v>
+        <v>125022727</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620301</v>
+        <v>620448</v>
       </c>
       <c r="R2" t="n">
-        <v>6659613</v>
+        <v>6659515</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125022973</v>
+        <v>125043872</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,7 +828,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -835,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620441</v>
+        <v>620309</v>
       </c>
       <c r="R3" t="n">
-        <v>6659571</v>
+        <v>6659619</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,11 +874,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023005</v>
+        <v>125022785</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,30 +912,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620453</v>
+        <v>620445</v>
       </c>
       <c r="R4" t="n">
-        <v>6659595</v>
+        <v>6659540</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,6 +980,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125044170</v>
+        <v>125043766</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1024,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620319</v>
+        <v>620301</v>
       </c>
       <c r="R5" t="n">
-        <v>6659768</v>
+        <v>6659613</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillningskrokar på granlåga</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,6 +1105,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023589</v>
+        <v>125044062</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,31 +1136,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620458</v>
+        <v>620361</v>
       </c>
       <c r="R6" t="n">
-        <v>6659607</v>
+        <v>6659725</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,11 +1203,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125044275</v>
+        <v>125022973</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,31 +1242,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1279,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620236</v>
+        <v>620441</v>
       </c>
       <c r="R7" t="n">
-        <v>6659797</v>
+        <v>6659571</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1318,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,7 +1327,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1459,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125044430</v>
+        <v>125023005</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,31 +1473,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620191</v>
+        <v>620453</v>
       </c>
       <c r="R9" t="n">
-        <v>6659731</v>
+        <v>6659595</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1551,6 +1544,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023241</v>
+        <v>125043140</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,42 +1575,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620459</v>
+        <v>620353</v>
       </c>
       <c r="R10" t="n">
-        <v>6659598</v>
+        <v>6659629</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,17 +1645,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spillning vid välta</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1680,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125044360</v>
+        <v>125044430</v>
       </c>
       <c r="B11" t="n">
-        <v>95598</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,31 +1682,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1724,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620199</v>
+        <v>620191</v>
       </c>
       <c r="R11" t="n">
-        <v>6659797</v>
+        <v>6659731</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1762,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1787,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125043140</v>
+        <v>125023241</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,42 +1792,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620353</v>
+        <v>620459</v>
       </c>
       <c r="R12" t="n">
-        <v>6659629</v>
+        <v>6659598</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,13 +1862,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillning vid välta</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1894,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125043272</v>
+        <v>125044170</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,25 +1903,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,7 +1929,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1942,10 +1939,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620344</v>
+        <v>620319</v>
       </c>
       <c r="R13" t="n">
-        <v>6659640</v>
+        <v>6659768</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1978,6 +1975,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125044062</v>
+        <v>125023589</v>
       </c>
       <c r="B14" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,30 +2018,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2047,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620361</v>
+        <v>620458</v>
       </c>
       <c r="R14" t="n">
-        <v>6659725</v>
+        <v>6659607</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2083,6 +2086,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023165</v>
+        <v>125024178</v>
       </c>
       <c r="B15" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2122,25 +2130,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620463</v>
+        <v>620466</v>
       </c>
       <c r="R15" t="n">
-        <v>6659593</v>
+        <v>6659617</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2194,7 +2202,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flertal plantor på väg i blom</t>
+          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,7 +2230,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125043872</v>
+        <v>125043272</v>
       </c>
       <c r="B16" t="n">
         <v>57666</v>
@@ -2260,7 +2268,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2270,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620309</v>
+        <v>620344</v>
       </c>
       <c r="R16" t="n">
-        <v>6659619</v>
+        <v>6659640</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023498</v>
+        <v>125044275</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,35 +2352,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2380,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620453</v>
+        <v>620236</v>
       </c>
       <c r="R17" t="n">
-        <v>6659605</v>
+        <v>6659797</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2420,7 +2424,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Sjöng från gran, se bild</t>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2429,6 +2433,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2447,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125022727</v>
+        <v>125023165</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>105117</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2463,31 +2468,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2495,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620448</v>
+        <v>620463</v>
       </c>
       <c r="R18" t="n">
-        <v>6659515</v>
+        <v>6659593</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2535,7 +2536,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Spillningshög under gran</t>
+          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,6 +2545,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2669,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125024178</v>
+        <v>125044360</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>95598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,25 +2683,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620466</v>
+        <v>620199</v>
       </c>
       <c r="R20" t="n">
-        <v>6659617</v>
+        <v>6659797</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2749,11 +2751,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125022785</v>
+        <v>125023498</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,31 +2790,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2825,10 +2826,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620445</v>
+        <v>620453</v>
       </c>
       <c r="R21" t="n">
-        <v>6659540</v>
+        <v>6659605</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2865,7 +2866,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Sjöng från gran, se bild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,7 +2875,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125043272</v>
+        <v>125044275</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,35 +2242,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2278,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620344</v>
+        <v>620236</v>
       </c>
       <c r="R16" t="n">
-        <v>6659640</v>
+        <v>6659797</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2316,12 +2312,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2340,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125044275</v>
+        <v>125043272</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2352,31 +2354,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2384,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620236</v>
+        <v>620344</v>
       </c>
       <c r="R17" t="n">
-        <v>6659797</v>
+        <v>6659640</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2422,18 +2428,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Cirka 20 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125022727</v>
+        <v>125022973</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620448</v>
+        <v>620441</v>
       </c>
       <c r="R2" t="n">
-        <v>6659515</v>
+        <v>6659571</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillningshög under gran</t>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125043872</v>
+        <v>125023165</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620309</v>
+        <v>620463</v>
       </c>
       <c r="R3" t="n">
-        <v>6659619</v>
+        <v>6659593</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,12 +872,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flertal plantor på väg i blom</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125022785</v>
+        <v>125044275</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -944,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620445</v>
+        <v>620236</v>
       </c>
       <c r="R4" t="n">
-        <v>6659540</v>
+        <v>6659797</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125043766</v>
+        <v>125022727</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,31 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620301</v>
+        <v>620448</v>
       </c>
       <c r="R5" t="n">
-        <v>6659613</v>
+        <v>6659515</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1102,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,7 +1111,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125044062</v>
+        <v>125044430</v>
       </c>
       <c r="B6" t="n">
-        <v>74840</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,30 +1141,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620361</v>
+        <v>620191</v>
       </c>
       <c r="R6" t="n">
-        <v>6659725</v>
+        <v>6659731</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,7 +1221,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125022973</v>
+        <v>125043922</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,35 +1251,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1278,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620441</v>
+        <v>620311</v>
       </c>
       <c r="R7" t="n">
-        <v>6659571</v>
+        <v>6659658</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1318,7 +1323,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>4 spillningskrokar</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,6 +1332,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1345,7 +1351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125043922</v>
+        <v>125023589</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1389,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620311</v>
+        <v>620458</v>
       </c>
       <c r="R8" t="n">
-        <v>6659658</v>
+        <v>6659607</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,7 +1435,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023005</v>
+        <v>125023241</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,30 +1475,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1500,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620453</v>
+        <v>620459</v>
       </c>
       <c r="R9" t="n">
-        <v>6659595</v>
+        <v>6659598</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,13 +1545,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spillning vid välta</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1670,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125044430</v>
+        <v>125044170</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,25 +1693,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,7 +1719,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1718,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620191</v>
+        <v>620319</v>
       </c>
       <c r="R11" t="n">
-        <v>6659731</v>
+        <v>6659768</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1754,6 +1765,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023241</v>
+        <v>125022785</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,31 +1808,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1824,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620459</v>
+        <v>620445</v>
       </c>
       <c r="R12" t="n">
-        <v>6659598</v>
+        <v>6659540</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spillning vid välta</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,6 +1889,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1891,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125044170</v>
+        <v>125043295</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>95598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,31 +1924,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1939,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620319</v>
+        <v>620324</v>
       </c>
       <c r="R13" t="n">
-        <v>6659768</v>
+        <v>6659626</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1977,17 +1990,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillningskrokar på granlåga</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2006,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023589</v>
+        <v>125043872</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2018,31 +2027,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2050,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620458</v>
+        <v>620309</v>
       </c>
       <c r="R14" t="n">
-        <v>6659607</v>
+        <v>6659619</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2088,18 +2101,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2118,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125024178</v>
+        <v>125044062</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,31 +2137,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2162,10 +2168,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620466</v>
+        <v>620361</v>
       </c>
       <c r="R15" t="n">
-        <v>6659617</v>
+        <v>6659725</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2198,11 +2204,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,7 +2231,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125044275</v>
+        <v>125024178</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2274,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620236</v>
+        <v>620466</v>
       </c>
       <c r="R16" t="n">
-        <v>6659797</v>
+        <v>6659617</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2314,7 +2315,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125043272</v>
+        <v>125044360</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>95598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2354,35 +2355,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2390,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620344</v>
+        <v>620199</v>
       </c>
       <c r="R17" t="n">
-        <v>6659640</v>
+        <v>6659797</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,6 +2431,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2452,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023165</v>
+        <v>125023498</v>
       </c>
       <c r="B18" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,31 +2462,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2496,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620463</v>
+        <v>620453</v>
       </c>
       <c r="R18" t="n">
-        <v>6659593</v>
+        <v>6659605</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2536,7 +2538,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flertal plantor på väg i blom</t>
+          <t>Sjöng från gran, se bild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,7 +2547,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2564,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125043295</v>
+        <v>125043766</v>
       </c>
       <c r="B19" t="n">
-        <v>95598</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,25 +2577,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620324</v>
+        <v>620301</v>
       </c>
       <c r="R19" t="n">
-        <v>6659626</v>
+        <v>6659613</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2644,6 +2645,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125044360</v>
+        <v>125043272</v>
       </c>
       <c r="B20" t="n">
-        <v>95598</v>
+        <v>57666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,31 +2689,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2715,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620199</v>
+        <v>620344</v>
       </c>
       <c r="R20" t="n">
-        <v>6659797</v>
+        <v>6659640</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2759,7 +2769,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2778,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023498</v>
+        <v>125023005</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2794,31 +2803,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,7 +2833,7 @@
         <v>620453</v>
       </c>
       <c r="R21" t="n">
-        <v>6659605</v>
+        <v>6659595</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2864,17 +2868,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Sjöng från gran, se bild</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125022973</v>
+        <v>125022727</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620441</v>
+        <v>620448</v>
       </c>
       <c r="R2" t="n">
-        <v>6659571</v>
+        <v>6659515</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>4 spillningskrokar</t>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125023165</v>
+        <v>125043272</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620463</v>
+        <v>620344</v>
       </c>
       <c r="R3" t="n">
-        <v>6659593</v>
+        <v>6659640</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,18 +876,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flertal plantor på väg i blom</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125044275</v>
+        <v>125044360</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>95598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,7 +944,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620236</v>
+        <v>620199</v>
       </c>
       <c r="R4" t="n">
         <v>6659797</v>
@@ -982,11 +980,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125022727</v>
+        <v>125023498</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,25 +1019,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,7 +1045,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620448</v>
+        <v>620453</v>
       </c>
       <c r="R5" t="n">
-        <v>6659515</v>
+        <v>6659605</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1102,7 +1095,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillningshög under gran</t>
+          <t>Sjöng från gran, se bild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125044430</v>
+        <v>125023589</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,35 +1134,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1177,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620191</v>
+        <v>620458</v>
       </c>
       <c r="R6" t="n">
-        <v>6659731</v>
+        <v>6659607</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1215,12 +1204,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125043922</v>
+        <v>125044275</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1283,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620311</v>
+        <v>620236</v>
       </c>
       <c r="R7" t="n">
-        <v>6659658</v>
+        <v>6659797</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1323,7 +1318,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023589</v>
+        <v>125043295</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>95598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,25 +1358,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620458</v>
+        <v>620324</v>
       </c>
       <c r="R8" t="n">
-        <v>6659607</v>
+        <v>6659626</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,11 +1426,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1681,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125044170</v>
+        <v>125043922</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,35 +1683,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1729,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620319</v>
+        <v>620311</v>
       </c>
       <c r="R11" t="n">
-        <v>6659768</v>
+        <v>6659658</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1769,7 +1755,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spillningskrokar på granlåga</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,6 +1764,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1796,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125022785</v>
+        <v>125023165</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,25 +1795,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620445</v>
+        <v>620463</v>
       </c>
       <c r="R12" t="n">
-        <v>6659540</v>
+        <v>6659593</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1867,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125043295</v>
+        <v>125044170</v>
       </c>
       <c r="B13" t="n">
-        <v>95598</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,27 +1911,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1952,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620324</v>
+        <v>620319</v>
       </c>
       <c r="R13" t="n">
-        <v>6659626</v>
+        <v>6659768</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1990,13 +1981,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillningskrokar på granlåga</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2015,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125043872</v>
+        <v>125024178</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,35 +2022,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2063,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620309</v>
+        <v>620466</v>
       </c>
       <c r="R14" t="n">
-        <v>6659619</v>
+        <v>6659617</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2101,12 +2092,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>cirka 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2125,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125044062</v>
+        <v>125044430</v>
       </c>
       <c r="B15" t="n">
-        <v>74840</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,30 +2134,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2168,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620361</v>
+        <v>620191</v>
       </c>
       <c r="R15" t="n">
-        <v>6659725</v>
+        <v>6659731</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2212,7 +2214,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2231,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125024178</v>
+        <v>125023005</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2243,31 +2244,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620466</v>
+        <v>620453</v>
       </c>
       <c r="R16" t="n">
-        <v>6659617</v>
+        <v>6659595</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2311,11 +2311,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125044360</v>
+        <v>125044062</v>
       </c>
       <c r="B17" t="n">
-        <v>95598</v>
+        <v>74840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,27 +2354,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2387,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620199</v>
+        <v>620361</v>
       </c>
       <c r="R17" t="n">
-        <v>6659797</v>
+        <v>6659725</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023498</v>
+        <v>125022973</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2462,25 +2456,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2488,7 +2482,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2498,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620453</v>
+        <v>620441</v>
       </c>
       <c r="R18" t="n">
-        <v>6659605</v>
+        <v>6659571</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2538,7 +2532,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Sjöng från gran, se bild</t>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,7 +2559,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125043766</v>
+        <v>125022785</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2609,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620301</v>
+        <v>620445</v>
       </c>
       <c r="R19" t="n">
-        <v>6659613</v>
+        <v>6659540</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2649,7 +2643,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125043272</v>
+        <v>125043766</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2689,35 +2683,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2725,10 +2715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620344</v>
+        <v>620301</v>
       </c>
       <c r="R20" t="n">
-        <v>6659640</v>
+        <v>6659613</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2763,12 +2753,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2787,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023005</v>
+        <v>125043872</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2803,26 +2799,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2830,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620453</v>
+        <v>620309</v>
       </c>
       <c r="R21" t="n">
-        <v>6659595</v>
+        <v>6659619</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2874,7 +2875,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023241</v>
+        <v>125043140</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,42 +1465,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620459</v>
+        <v>620353</v>
       </c>
       <c r="R9" t="n">
-        <v>6659598</v>
+        <v>6659629</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1535,17 +1535,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillning vid välta</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1564,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125043140</v>
+        <v>125043922</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1604,14 +1600,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620353</v>
+        <v>620311</v>
       </c>
       <c r="R10" t="n">
-        <v>6659629</v>
+        <v>6659658</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,6 +1640,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125043922</v>
+        <v>125023165</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,25 +1684,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,10 +1716,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620311</v>
+        <v>620463</v>
       </c>
       <c r="R11" t="n">
-        <v>6659658</v>
+        <v>6659593</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1755,7 +1756,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023165</v>
+        <v>125023241</v>
       </c>
       <c r="B12" t="n">
-        <v>105117</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,27 +1800,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1827,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620463</v>
+        <v>620459</v>
       </c>
       <c r="R12" t="n">
-        <v>6659593</v>
+        <v>6659598</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1867,7 +1868,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flertal plantor på väg i blom</t>
+          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,7 +1877,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125022785</v>
+        <v>125043872</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,31 +2571,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2603,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620445</v>
+        <v>620309</v>
       </c>
       <c r="R19" t="n">
-        <v>6659540</v>
+        <v>6659619</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2641,18 +2645,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2671,7 +2669,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125043766</v>
+        <v>125022785</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2715,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620301</v>
+        <v>620445</v>
       </c>
       <c r="R20" t="n">
-        <v>6659613</v>
+        <v>6659540</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2755,7 +2753,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125043872</v>
+        <v>125043766</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2795,35 +2793,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620309</v>
+        <v>620301</v>
       </c>
       <c r="R21" t="n">
-        <v>6659619</v>
+        <v>6659613</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2869,12 +2863,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125043140</v>
+        <v>125023241</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,42 +1465,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620353</v>
+        <v>620459</v>
       </c>
       <c r="R9" t="n">
-        <v>6659629</v>
+        <v>6659598</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1535,13 +1535,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spillning vid välta</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1560,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125043922</v>
+        <v>125043140</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1600,14 +1604,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620311</v>
+        <v>620353</v>
       </c>
       <c r="R10" t="n">
-        <v>6659658</v>
+        <v>6659629</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1640,11 +1644,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023165</v>
+        <v>125043922</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,25 +1683,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1716,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620463</v>
+        <v>620311</v>
       </c>
       <c r="R11" t="n">
-        <v>6659593</v>
+        <v>6659658</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1756,7 +1755,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flertal plantor på väg i blom</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023241</v>
+        <v>125023165</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>105117</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,27 +1799,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1828,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620459</v>
+        <v>620463</v>
       </c>
       <c r="R12" t="n">
-        <v>6659598</v>
+        <v>6659593</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1868,7 +1867,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spillning vid välta</t>
+          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,6 +1876,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125024178</v>
+        <v>125044430</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,31 +2022,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2054,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620466</v>
+        <v>620191</v>
       </c>
       <c r="R14" t="n">
-        <v>6659617</v>
+        <v>6659731</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2092,18 +2096,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>cirka 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2122,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125044430</v>
+        <v>125024178</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,35 +2132,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2170,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620191</v>
+        <v>620466</v>
       </c>
       <c r="R15" t="n">
-        <v>6659731</v>
+        <v>6659617</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2208,12 +2202,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>cirka 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125022727</v>
+        <v>125043922</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620448</v>
+        <v>620311</v>
       </c>
       <c r="R2" t="n">
-        <v>6659515</v>
+        <v>6659658</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillningshög under gran</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125043272</v>
+        <v>125043295</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>95598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620344</v>
+        <v>620324</v>
       </c>
       <c r="R3" t="n">
-        <v>6659640</v>
+        <v>6659626</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125044360</v>
+        <v>125023005</v>
       </c>
       <c r="B4" t="n">
-        <v>95598</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +906,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620199</v>
+        <v>620453</v>
       </c>
       <c r="R4" t="n">
-        <v>6659797</v>
+        <v>6659595</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023498</v>
+        <v>125022727</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,25 +1012,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,7 +1038,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1055,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620453</v>
+        <v>620448</v>
       </c>
       <c r="R5" t="n">
-        <v>6659605</v>
+        <v>6659515</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sjöng från gran, se bild</t>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023589</v>
+        <v>125022973</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,31 +1127,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620458</v>
+        <v>620441</v>
       </c>
       <c r="R6" t="n">
-        <v>6659607</v>
+        <v>6659571</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,7 +1203,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1212,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1234,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125044275</v>
+        <v>125044170</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,31 +1242,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620236</v>
+        <v>620319</v>
       </c>
       <c r="R7" t="n">
-        <v>6659797</v>
+        <v>6659768</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1346,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125043295</v>
+        <v>125044062</v>
       </c>
       <c r="B8" t="n">
-        <v>95598</v>
+        <v>74840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,27 +1361,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1390,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620324</v>
+        <v>620361</v>
       </c>
       <c r="R8" t="n">
-        <v>6659626</v>
+        <v>6659725</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1453,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023241</v>
+        <v>125043766</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,31 +1463,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620459</v>
+        <v>620301</v>
       </c>
       <c r="R9" t="n">
-        <v>6659598</v>
+        <v>6659613</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1537,7 +1535,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spillning vid välta</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,6 +1544,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1564,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125043140</v>
+        <v>125044275</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1604,14 +1603,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620353</v>
+        <v>620236</v>
       </c>
       <c r="R10" t="n">
-        <v>6659629</v>
+        <v>6659797</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,6 +1643,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125043922</v>
+        <v>125043272</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,31 +1687,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1715,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620311</v>
+        <v>620344</v>
       </c>
       <c r="R11" t="n">
-        <v>6659658</v>
+        <v>6659640</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,18 +1761,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1783,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023165</v>
+        <v>125043140</v>
       </c>
       <c r="B12" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1823,14 +1825,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620463</v>
+        <v>620353</v>
       </c>
       <c r="R12" t="n">
-        <v>6659593</v>
+        <v>6659629</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1863,11 +1865,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125044170</v>
+        <v>125044360</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>95598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,31 +1908,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620319</v>
+        <v>620199</v>
       </c>
       <c r="R13" t="n">
-        <v>6659768</v>
+        <v>6659797</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1981,17 +1974,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillningskrokar på granlåga</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2010,7 +1999,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125044430</v>
+        <v>125043872</v>
       </c>
       <c r="B14" t="n">
         <v>57666</v>
@@ -2058,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620191</v>
+        <v>620309</v>
       </c>
       <c r="R14" t="n">
-        <v>6659731</v>
+        <v>6659619</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2120,7 +2109,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125024178</v>
+        <v>125022785</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2164,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620466</v>
+        <v>620445</v>
       </c>
       <c r="R15" t="n">
-        <v>6659617</v>
+        <v>6659540</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2204,7 +2193,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>cirka 30 bladrosetter</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023005</v>
+        <v>125023498</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,26 +2237,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2278,7 +2272,7 @@
         <v>620453</v>
       </c>
       <c r="R16" t="n">
-        <v>6659595</v>
+        <v>6659605</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2313,13 +2307,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sjöng från gran, se bild</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2338,10 +2336,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125044062</v>
+        <v>125023165</v>
       </c>
       <c r="B17" t="n">
-        <v>74840</v>
+        <v>105117</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2354,26 +2352,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2381,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620361</v>
+        <v>620463</v>
       </c>
       <c r="R17" t="n">
-        <v>6659725</v>
+        <v>6659593</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2417,6 +2416,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125022973</v>
+        <v>125023589</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2456,35 +2460,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620441</v>
+        <v>620458</v>
       </c>
       <c r="R18" t="n">
-        <v>6659571</v>
+        <v>6659607</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>4 spillningskrokar</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2541,6 +2541,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2559,7 +2560,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125043872</v>
+        <v>125044430</v>
       </c>
       <c r="B19" t="n">
         <v>57666</v>
@@ -2607,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620309</v>
+        <v>620191</v>
       </c>
       <c r="R19" t="n">
-        <v>6659619</v>
+        <v>6659731</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125022785</v>
+        <v>125023241</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,31 +2682,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2713,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620445</v>
+        <v>620459</v>
       </c>
       <c r="R20" t="n">
-        <v>6659540</v>
+        <v>6659598</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2753,7 +2754,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,7 +2763,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125043766</v>
+        <v>125024178</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620301</v>
+        <v>620466</v>
       </c>
       <c r="R21" t="n">
-        <v>6659613</v>
+        <v>6659617</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125043922</v>
+        <v>125023005</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620311</v>
+        <v>620453</v>
       </c>
       <c r="R2" t="n">
-        <v>6659658</v>
+        <v>6659595</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125043295</v>
+        <v>125044062</v>
       </c>
       <c r="B3" t="n">
-        <v>95598</v>
+        <v>74840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,27 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620324</v>
+        <v>620361</v>
       </c>
       <c r="R3" t="n">
-        <v>6659626</v>
+        <v>6659725</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -894,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125023005</v>
+        <v>125043140</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,41 +899,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620453</v>
+        <v>620353</v>
       </c>
       <c r="R4" t="n">
-        <v>6659595</v>
+        <v>6659629</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125022727</v>
+        <v>125022785</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,35 +1006,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620448</v>
+        <v>620445</v>
       </c>
       <c r="R5" t="n">
-        <v>6659515</v>
+        <v>6659540</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,7 +1078,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillningshög under gran</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125022973</v>
+        <v>125044170</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1163,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620441</v>
+        <v>620319</v>
       </c>
       <c r="R6" t="n">
-        <v>6659571</v>
+        <v>6659768</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4 spillningskrokar</t>
+          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125044170</v>
+        <v>125023241</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1266,11 +1257,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1278,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620319</v>
+        <v>620459</v>
       </c>
       <c r="R7" t="n">
-        <v>6659768</v>
+        <v>6659598</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1318,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spillningskrokar på granlåga</t>
+          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125044062</v>
+        <v>125043872</v>
       </c>
       <c r="B8" t="n">
-        <v>74840</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,30 +1344,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620361</v>
+        <v>620309</v>
       </c>
       <c r="R8" t="n">
-        <v>6659725</v>
+        <v>6659619</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1424,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1451,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125043766</v>
+        <v>125043922</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1495,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620301</v>
+        <v>620311</v>
       </c>
       <c r="R9" t="n">
-        <v>6659613</v>
+        <v>6659658</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1535,7 +1526,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125043272</v>
+        <v>125022727</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,25 +1678,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,7 +1704,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1723,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620344</v>
+        <v>620448</v>
       </c>
       <c r="R11" t="n">
-        <v>6659640</v>
+        <v>6659515</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1759,6 +1750,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1781,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125043140</v>
+        <v>125023589</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1825,14 +1821,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620353</v>
+        <v>620458</v>
       </c>
       <c r="R12" t="n">
-        <v>6659629</v>
+        <v>6659607</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1865,6 +1861,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,10 +2000,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125043872</v>
+        <v>125022973</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,25 +2012,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2037,7 +2038,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2047,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620309</v>
+        <v>620441</v>
       </c>
       <c r="R14" t="n">
-        <v>6659619</v>
+        <v>6659571</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2083,6 +2084,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125022785</v>
+        <v>125044430</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,31 +2127,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2153,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620445</v>
+        <v>620191</v>
       </c>
       <c r="R15" t="n">
-        <v>6659540</v>
+        <v>6659731</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2191,18 +2201,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2221,10 +2225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023498</v>
+        <v>125023165</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,35 +2237,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620453</v>
+        <v>620463</v>
       </c>
       <c r="R16" t="n">
-        <v>6659605</v>
+        <v>6659593</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Sjöng från gran, se bild</t>
+          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,6 +2318,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2336,10 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023165</v>
+        <v>125043766</v>
       </c>
       <c r="B17" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2348,25 +2349,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620463</v>
+        <v>620301</v>
       </c>
       <c r="R17" t="n">
-        <v>6659593</v>
+        <v>6659613</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2420,7 +2421,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Flertal plantor på väg i blom</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,10 +2449,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023589</v>
+        <v>125043272</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,31 +2461,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2492,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620458</v>
+        <v>620344</v>
       </c>
       <c r="R18" t="n">
-        <v>6659607</v>
+        <v>6659640</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2530,18 +2535,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2560,7 +2559,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125044430</v>
+        <v>125023498</v>
       </c>
       <c r="B19" t="n">
         <v>57666</v>
@@ -2608,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620191</v>
+        <v>620453</v>
       </c>
       <c r="R19" t="n">
-        <v>6659731</v>
+        <v>6659605</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2644,6 +2643,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sjöng från gran, se bild</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2670,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125023241</v>
+        <v>125043295</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>95598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,27 +2690,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2714,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620459</v>
+        <v>620324</v>
       </c>
       <c r="R20" t="n">
-        <v>6659598</v>
+        <v>6659626</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2752,17 +2756,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Spillning vid välta</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125023005</v>
+        <v>125044170</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620453</v>
+        <v>620319</v>
       </c>
       <c r="R2" t="n">
-        <v>6659595</v>
+        <v>6659768</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,13 +761,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spillningskrokar på granlåga</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125044062</v>
+        <v>125022785</v>
       </c>
       <c r="B3" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620361</v>
+        <v>620445</v>
       </c>
       <c r="R3" t="n">
-        <v>6659725</v>
+        <v>6659540</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,6 +870,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125043140</v>
+        <v>125044430</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,42 +914,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620353</v>
+        <v>620191</v>
       </c>
       <c r="R4" t="n">
-        <v>6659629</v>
+        <v>6659731</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,7 +994,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125022785</v>
+        <v>125044360</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>95598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1024,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620445</v>
+        <v>620199</v>
       </c>
       <c r="R5" t="n">
-        <v>6659540</v>
+        <v>6659797</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1074,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125044170</v>
+        <v>125043872</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,7 +1157,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1154,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620319</v>
+        <v>620309</v>
       </c>
       <c r="R6" t="n">
-        <v>6659768</v>
+        <v>6659619</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,11 +1203,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125023241</v>
+        <v>125043272</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,31 +1241,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620459</v>
+        <v>620344</v>
       </c>
       <c r="R7" t="n">
-        <v>6659598</v>
+        <v>6659640</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1301,11 +1313,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1339,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125043872</v>
+        <v>125023498</v>
       </c>
       <c r="B8" t="n">
         <v>57666</v>
@@ -1380,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620309</v>
+        <v>620453</v>
       </c>
       <c r="R8" t="n">
-        <v>6659619</v>
+        <v>6659605</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1416,6 +1423,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sjöng från gran, se bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125043922</v>
+        <v>125023589</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1486,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620311</v>
+        <v>620458</v>
       </c>
       <c r="R9" t="n">
-        <v>6659658</v>
+        <v>6659607</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1526,7 +1538,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125044275</v>
+        <v>125022973</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,31 +1578,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1598,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620236</v>
+        <v>620441</v>
       </c>
       <c r="R10" t="n">
-        <v>6659797</v>
+        <v>6659571</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,7 +1654,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,7 +1663,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1666,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125022727</v>
+        <v>125023165</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,31 +1697,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1714,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620448</v>
+        <v>620463</v>
       </c>
       <c r="R11" t="n">
-        <v>6659515</v>
+        <v>6659593</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1754,7 +1765,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spillningshög under gran</t>
+          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,6 +1774,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1781,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023589</v>
+        <v>125044062</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,31 +1805,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1825,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620458</v>
+        <v>620361</v>
       </c>
       <c r="R12" t="n">
-        <v>6659607</v>
+        <v>6659725</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1861,11 +1872,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125044360</v>
+        <v>125024178</v>
       </c>
       <c r="B13" t="n">
-        <v>95598</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,25 +1911,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620199</v>
+        <v>620466</v>
       </c>
       <c r="R13" t="n">
-        <v>6659797</v>
+        <v>6659617</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1973,6 +1979,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125022973</v>
+        <v>125043295</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>95598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,31 +2027,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2048,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620441</v>
+        <v>620324</v>
       </c>
       <c r="R14" t="n">
-        <v>6659571</v>
+        <v>6659626</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2086,17 +2093,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>4 spillningskrokar</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2115,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125044430</v>
+        <v>125023005</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,31 +2134,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2163,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620191</v>
+        <v>620453</v>
       </c>
       <c r="R15" t="n">
-        <v>6659731</v>
+        <v>6659595</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2207,6 +2205,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2225,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023165</v>
+        <v>125022727</v>
       </c>
       <c r="B16" t="n">
-        <v>105117</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,27 +2240,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2269,10 +2272,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620463</v>
+        <v>620448</v>
       </c>
       <c r="R16" t="n">
-        <v>6659593</v>
+        <v>6659515</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2309,7 +2312,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flertal plantor på väg i blom</t>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,7 +2321,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2337,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125043766</v>
+        <v>125023241</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2349,31 +2351,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2381,10 +2383,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620301</v>
+        <v>620459</v>
       </c>
       <c r="R17" t="n">
-        <v>6659613</v>
+        <v>6659598</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2421,7 +2423,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,7 +2432,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2449,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125043272</v>
+        <v>125043922</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,35 +2462,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2497,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620344</v>
+        <v>620311</v>
       </c>
       <c r="R18" t="n">
-        <v>6659640</v>
+        <v>6659658</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2535,12 +2532,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>mer än 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2559,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023498</v>
+        <v>125043766</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,35 +2574,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2607,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620453</v>
+        <v>620301</v>
       </c>
       <c r="R19" t="n">
-        <v>6659605</v>
+        <v>6659613</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2647,7 +2646,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Sjöng från gran, se bild</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2656,6 +2655,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125043295</v>
+        <v>125043140</v>
       </c>
       <c r="B20" t="n">
-        <v>95598</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,25 +2686,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2714,14 +2714,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620324</v>
+        <v>620353</v>
       </c>
       <c r="R20" t="n">
-        <v>6659626</v>
+        <v>6659629</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125024178</v>
+        <v>125044275</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620466</v>
+        <v>620236</v>
       </c>
       <c r="R21" t="n">
-        <v>6659617</v>
+        <v>6659797</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>cirka 30 bladrosetter</t>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125022785</v>
+        <v>125044430</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620445</v>
+        <v>620191</v>
       </c>
       <c r="R3" t="n">
-        <v>6659540</v>
+        <v>6659731</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,18 +876,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125044430</v>
+        <v>125022785</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,35 +912,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620191</v>
+        <v>620445</v>
       </c>
       <c r="R4" t="n">
-        <v>6659731</v>
+        <v>6659540</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,12 +982,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>mer än 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125044170</v>
+        <v>125044360</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>95598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620319</v>
+        <v>620199</v>
       </c>
       <c r="R2" t="n">
-        <v>6659768</v>
+        <v>6659797</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,17 +757,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillningskrokar på granlåga</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125044430</v>
+        <v>125023165</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620191</v>
+        <v>620463</v>
       </c>
       <c r="R3" t="n">
-        <v>6659731</v>
+        <v>6659593</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,12 +864,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flertal plantor på väg i blom</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125022785</v>
+        <v>125022727</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +906,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620445</v>
+        <v>620448</v>
       </c>
       <c r="R4" t="n">
-        <v>6659540</v>
+        <v>6659515</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +982,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,7 +991,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125044360</v>
+        <v>125043922</v>
       </c>
       <c r="B5" t="n">
-        <v>95598</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620199</v>
+        <v>620311</v>
       </c>
       <c r="R5" t="n">
-        <v>6659797</v>
+        <v>6659658</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,6 +1089,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125043872</v>
+        <v>125044275</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,35 +1133,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620309</v>
+        <v>620236</v>
       </c>
       <c r="R6" t="n">
-        <v>6659619</v>
+        <v>6659797</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,12 +1203,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1229,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125043272</v>
+        <v>125043872</v>
       </c>
       <c r="B7" t="n">
         <v>57666</v>
@@ -1267,7 +1271,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1277,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620344</v>
+        <v>620309</v>
       </c>
       <c r="R7" t="n">
-        <v>6659640</v>
+        <v>6659619</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023498</v>
+        <v>125044062</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>74840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,35 +1355,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1387,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620453</v>
+        <v>620361</v>
       </c>
       <c r="R8" t="n">
-        <v>6659605</v>
+        <v>6659725</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1425,17 +1424,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Sjöng från gran, se bild</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1566,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125022973</v>
+        <v>125043140</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,46 +1573,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620441</v>
+        <v>620353</v>
       </c>
       <c r="R10" t="n">
-        <v>6659571</v>
+        <v>6659629</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1652,17 +1643,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4 spillningskrokar</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023165</v>
+        <v>125023005</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,31 +1680,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1725,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620463</v>
+        <v>620453</v>
       </c>
       <c r="R11" t="n">
-        <v>6659593</v>
+        <v>6659595</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1761,11 +1747,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,10 +1774,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125044062</v>
+        <v>125044170</v>
       </c>
       <c r="B12" t="n">
-        <v>74840</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,26 +1790,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620361</v>
+        <v>620319</v>
       </c>
       <c r="R12" t="n">
-        <v>6659725</v>
+        <v>6659768</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1874,13 +1860,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillningskrokar på granlåga</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1899,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125024178</v>
+        <v>125043295</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>95598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,25 +1901,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1933,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620466</v>
+        <v>620324</v>
       </c>
       <c r="R13" t="n">
-        <v>6659617</v>
+        <v>6659626</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1979,11 +1969,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,10 +1996,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125043295</v>
+        <v>125023241</v>
       </c>
       <c r="B14" t="n">
-        <v>95598</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,27 +2012,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2055,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620324</v>
+        <v>620459</v>
       </c>
       <c r="R14" t="n">
-        <v>6659626</v>
+        <v>6659598</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2093,13 +2078,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spillning vid välta</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2118,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023005</v>
+        <v>125044430</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,26 +2123,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2161,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620453</v>
+        <v>620191</v>
       </c>
       <c r="R15" t="n">
-        <v>6659595</v>
+        <v>6659731</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2205,7 +2199,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2224,10 +2217,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125022727</v>
+        <v>125022785</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,35 +2229,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2272,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620448</v>
+        <v>620445</v>
       </c>
       <c r="R16" t="n">
-        <v>6659515</v>
+        <v>6659540</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2312,7 +2301,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spillningshög under gran</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,6 +2310,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2339,10 +2329,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125023241</v>
+        <v>125043272</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,31 +2341,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2383,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620459</v>
+        <v>620344</v>
       </c>
       <c r="R17" t="n">
-        <v>6659598</v>
+        <v>6659640</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2419,11 +2413,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,7 +2439,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125043922</v>
+        <v>125043766</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2494,10 +2483,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620311</v>
+        <v>620301</v>
       </c>
       <c r="R18" t="n">
-        <v>6659658</v>
+        <v>6659613</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2534,7 +2523,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,7 +2551,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125043766</v>
+        <v>125024178</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2606,10 +2595,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620301</v>
+        <v>620466</v>
       </c>
       <c r="R19" t="n">
-        <v>6659613</v>
+        <v>6659617</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2646,7 +2635,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125043140</v>
+        <v>125022973</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,42 +2675,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620353</v>
+        <v>620441</v>
       </c>
       <c r="R20" t="n">
-        <v>6659629</v>
+        <v>6659571</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2756,13 +2749,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>4 spillningskrokar</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2781,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125044275</v>
+        <v>125023498</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,31 +2790,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2825,10 +2826,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620236</v>
+        <v>620453</v>
       </c>
       <c r="R21" t="n">
-        <v>6659797</v>
+        <v>6659605</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2865,7 +2866,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>Sjöng från gran, se bild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,7 +2875,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125043140</v>
+        <v>125023005</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,42 +1573,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620353</v>
+        <v>620453</v>
       </c>
       <c r="R10" t="n">
-        <v>6659629</v>
+        <v>6659595</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1668,10 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125023005</v>
+        <v>125043140</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,41 +1679,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620453</v>
+        <v>620353</v>
       </c>
       <c r="R11" t="n">
-        <v>6659595</v>
+        <v>6659629</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125044360</v>
+        <v>125022727</v>
       </c>
       <c r="B2" t="n">
-        <v>95598</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620199</v>
+        <v>620448</v>
       </c>
       <c r="R2" t="n">
-        <v>6659797</v>
+        <v>6659515</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,13 +761,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spillningshög under gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125023165</v>
+        <v>125043140</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620463</v>
+        <v>620353</v>
       </c>
       <c r="R3" t="n">
-        <v>6659593</v>
+        <v>6659629</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,11 +870,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125022727</v>
+        <v>125044275</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,35 +909,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620448</v>
+        <v>620236</v>
       </c>
       <c r="R4" t="n">
-        <v>6659515</v>
+        <v>6659797</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,7 +981,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillningshög under gran</t>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,6 +990,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125043922</v>
+        <v>125023589</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620311</v>
+        <v>620458</v>
       </c>
       <c r="R5" t="n">
-        <v>6659658</v>
+        <v>6659607</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125044275</v>
+        <v>125023241</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,31 +1133,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620236</v>
+        <v>620459</v>
       </c>
       <c r="R6" t="n">
-        <v>6659797</v>
+        <v>6659598</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1214,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125043872</v>
+        <v>125024178</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1244,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620309</v>
+        <v>620466</v>
       </c>
       <c r="R7" t="n">
-        <v>6659619</v>
+        <v>6659617</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,12 +1314,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>cirka 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125044062</v>
+        <v>125043766</v>
       </c>
       <c r="B8" t="n">
-        <v>74840</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,30 +1356,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1386,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620361</v>
+        <v>620301</v>
       </c>
       <c r="R8" t="n">
-        <v>6659725</v>
+        <v>6659613</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,6 +1424,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023589</v>
+        <v>125043872</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,31 +1468,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1493,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620458</v>
+        <v>620309</v>
       </c>
       <c r="R9" t="n">
-        <v>6659607</v>
+        <v>6659619</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1531,18 +1542,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1667,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125043140</v>
+        <v>125044430</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,42 +1684,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620353</v>
+        <v>620191</v>
       </c>
       <c r="R11" t="n">
-        <v>6659629</v>
+        <v>6659731</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1755,7 +1764,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1774,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125044170</v>
+        <v>125044360</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>95598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1790,31 +1798,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1822,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620319</v>
+        <v>620199</v>
       </c>
       <c r="R12" t="n">
-        <v>6659768</v>
+        <v>6659797</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1860,17 +1864,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spillningskrokar på granlåga</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125043295</v>
+        <v>125044170</v>
       </c>
       <c r="B13" t="n">
-        <v>95598</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,27 +1905,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1933,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620324</v>
+        <v>620319</v>
       </c>
       <c r="R13" t="n">
-        <v>6659626</v>
+        <v>6659768</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1971,13 +1975,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillningskrokar på granlåga</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1996,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023241</v>
+        <v>125043272</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,31 +2016,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2040,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620459</v>
+        <v>620344</v>
       </c>
       <c r="R14" t="n">
-        <v>6659598</v>
+        <v>6659640</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2076,11 +2088,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125044430</v>
+        <v>125023165</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,35 +2126,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620191</v>
+        <v>620463</v>
       </c>
       <c r="R15" t="n">
-        <v>6659731</v>
+        <v>6659593</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2193,12 +2196,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flertal plantor på väg i blom</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2217,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125022785</v>
+        <v>125044062</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>74840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,31 +2238,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2261,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620445</v>
+        <v>620361</v>
       </c>
       <c r="R16" t="n">
-        <v>6659540</v>
+        <v>6659725</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2297,11 +2305,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2329,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125043272</v>
+        <v>125022973</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,25 +2344,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,7 +2370,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2377,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620344</v>
+        <v>620441</v>
       </c>
       <c r="R17" t="n">
-        <v>6659640</v>
+        <v>6659571</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2413,6 +2416,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,7 +2447,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125043766</v>
+        <v>125043922</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2483,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620301</v>
+        <v>620311</v>
       </c>
       <c r="R18" t="n">
-        <v>6659613</v>
+        <v>6659658</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2523,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125024178</v>
+        <v>125023498</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2563,31 +2571,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2595,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620466</v>
+        <v>620453</v>
       </c>
       <c r="R19" t="n">
-        <v>6659617</v>
+        <v>6659605</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2635,7 +2647,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>cirka 30 bladrosetter</t>
+          <t>Sjöng från gran, se bild</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,7 +2656,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2663,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125022973</v>
+        <v>125022785</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,35 +2686,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2711,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620441</v>
+        <v>620445</v>
       </c>
       <c r="R20" t="n">
-        <v>6659571</v>
+        <v>6659540</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2751,7 +2758,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>4 spillningskrokar</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,6 +2767,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2778,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125023498</v>
+        <v>125043295</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>95598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2790,35 +2798,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>2170</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2826,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620453</v>
+        <v>620324</v>
       </c>
       <c r="R21" t="n">
-        <v>6659605</v>
+        <v>6659626</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2864,17 +2868,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Sjöng från gran, se bild</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125022727</v>
+        <v>125043295</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>95766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620448</v>
+        <v>620324</v>
       </c>
       <c r="R2" t="n">
-        <v>6659515</v>
+        <v>6659626</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,17 +757,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillningshög under gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125043140</v>
+        <v>125044430</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57793</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,42 +794,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620353</v>
+        <v>620191</v>
       </c>
       <c r="R3" t="n">
-        <v>6659629</v>
+        <v>6659731</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125044275</v>
+        <v>125022785</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620236</v>
+        <v>620445</v>
       </c>
       <c r="R4" t="n">
-        <v>6659797</v>
+        <v>6659540</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +976,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125023589</v>
+        <v>125022727</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,31 +1016,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620458</v>
+        <v>620448</v>
       </c>
       <c r="R5" t="n">
-        <v>6659607</v>
+        <v>6659515</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,7 +1092,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,7 +1101,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125023241</v>
+        <v>125044170</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,7 +1155,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620459</v>
+        <v>620319</v>
       </c>
       <c r="R6" t="n">
-        <v>6659598</v>
+        <v>6659768</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,7 +1207,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillning vid välta</t>
+          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125024178</v>
+        <v>125044360</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>95766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1246,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620466</v>
+        <v>620199</v>
       </c>
       <c r="R7" t="n">
-        <v>6659617</v>
+        <v>6659797</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,11 +1314,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125043766</v>
+        <v>125044275</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620301</v>
+        <v>620236</v>
       </c>
       <c r="R8" t="n">
-        <v>6659613</v>
+        <v>6659797</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1428,7 +1425,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125043872</v>
+        <v>125023589</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,35 +1465,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1504,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620309</v>
+        <v>620458</v>
       </c>
       <c r="R9" t="n">
-        <v>6659619</v>
+        <v>6659607</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1542,12 +1535,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1566,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023005</v>
+        <v>125043766</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,30 +1577,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620453</v>
+        <v>620301</v>
       </c>
       <c r="R10" t="n">
-        <v>6659595</v>
+        <v>6659613</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1645,6 +1645,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125044430</v>
+        <v>125043272</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1720,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620191</v>
+        <v>620344</v>
       </c>
       <c r="R11" t="n">
-        <v>6659731</v>
+        <v>6659640</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,10 +1787,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125044360</v>
+        <v>125023005</v>
       </c>
       <c r="B12" t="n">
-        <v>95598</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,31 +1799,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1826,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620199</v>
+        <v>620453</v>
       </c>
       <c r="R12" t="n">
-        <v>6659797</v>
+        <v>6659595</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1889,10 +1893,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125044170</v>
+        <v>125024178</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,35 +1905,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620319</v>
+        <v>620466</v>
       </c>
       <c r="R13" t="n">
-        <v>6659768</v>
+        <v>6659617</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spillningskrokar på granlåga</t>
+          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,6 +1986,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2004,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125043272</v>
+        <v>125022973</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>56836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2017,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2042,7 +2043,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2052,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620344</v>
+        <v>620441</v>
       </c>
       <c r="R14" t="n">
-        <v>6659640</v>
+        <v>6659571</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2088,6 +2089,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125023165</v>
+        <v>125043140</v>
       </c>
       <c r="B15" t="n">
-        <v>105117</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,25 +2132,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,14 +2160,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620463</v>
+        <v>620353</v>
       </c>
       <c r="R15" t="n">
-        <v>6659593</v>
+        <v>6659629</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2194,11 +2200,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,10 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125044062</v>
+        <v>125023498</v>
       </c>
       <c r="B16" t="n">
-        <v>74840</v>
+        <v>57793</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,30 +2239,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2269,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620361</v>
+        <v>620453</v>
       </c>
       <c r="R16" t="n">
-        <v>6659725</v>
+        <v>6659605</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2307,13 +2313,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sjöng från gran, se bild</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2332,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125022973</v>
+        <v>125043872</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57793</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,25 +2354,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,7 +2380,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2380,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620441</v>
+        <v>620309</v>
       </c>
       <c r="R17" t="n">
-        <v>6659571</v>
+        <v>6659619</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2416,11 +2426,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125043922</v>
+        <v>125023165</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>105293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620311</v>
+        <v>620463</v>
       </c>
       <c r="R18" t="n">
-        <v>6659658</v>
+        <v>6659593</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2531,7 +2536,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023498</v>
+        <v>125023241</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>56836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,35 +2576,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2607,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620453</v>
+        <v>620459</v>
       </c>
       <c r="R19" t="n">
-        <v>6659605</v>
+        <v>6659598</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2647,7 +2648,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Sjöng från gran, se bild</t>
+          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2675,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125022785</v>
+        <v>125043922</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,10 +2719,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620445</v>
+        <v>620311</v>
       </c>
       <c r="R20" t="n">
-        <v>6659540</v>
+        <v>6659658</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2786,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125043295</v>
+        <v>125044062</v>
       </c>
       <c r="B21" t="n">
-        <v>95598</v>
+        <v>74964</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2802,27 +2803,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620324</v>
+        <v>620361</v>
       </c>
       <c r="R21" t="n">
-        <v>6659626</v>
+        <v>6659725</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125043295</v>
+        <v>125023005</v>
       </c>
       <c r="B2" t="n">
-        <v>95766</v>
+        <v>91166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620324</v>
+        <v>620453</v>
       </c>
       <c r="R2" t="n">
-        <v>6659626</v>
+        <v>6659595</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125044430</v>
+        <v>125044275</v>
       </c>
       <c r="B3" t="n">
-        <v>57793</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620191</v>
+        <v>620236</v>
       </c>
       <c r="R3" t="n">
-        <v>6659731</v>
+        <v>6659797</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,12 +863,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125022785</v>
+        <v>125022727</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,31 +905,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620445</v>
+        <v>620448</v>
       </c>
       <c r="R4" t="n">
-        <v>6659540</v>
+        <v>6659515</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,7 +981,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,7 +990,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125022727</v>
+        <v>125043140</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,46 +1020,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620448</v>
+        <v>620353</v>
       </c>
       <c r="R5" t="n">
-        <v>6659515</v>
+        <v>6659629</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,17 +1090,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillningshög under gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125044170</v>
+        <v>125043766</v>
       </c>
       <c r="B6" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,35 +1127,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620319</v>
+        <v>620301</v>
       </c>
       <c r="R6" t="n">
-        <v>6659768</v>
+        <v>6659613</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1199,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillningskrokar på granlåga</t>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,6 +1208,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1341,7 +1334,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125044275</v>
+        <v>125023589</v>
       </c>
       <c r="B8" t="n">
         <v>98269</v>
@@ -1385,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620236</v>
+        <v>620458</v>
       </c>
       <c r="R8" t="n">
-        <v>6659797</v>
+        <v>6659607</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1425,7 +1418,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125023589</v>
+        <v>125043272</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>57793</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,31 +1458,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1497,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620458</v>
+        <v>620344</v>
       </c>
       <c r="R9" t="n">
-        <v>6659607</v>
+        <v>6659640</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1535,18 +1532,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1565,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125043766</v>
+        <v>125023241</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,31 +1568,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1609,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620301</v>
+        <v>620459</v>
       </c>
       <c r="R10" t="n">
-        <v>6659613</v>
+        <v>6659598</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1649,7 +1640,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,7 +1649,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1677,10 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125043272</v>
+        <v>125043922</v>
       </c>
       <c r="B11" t="n">
-        <v>57793</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,35 +1679,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1725,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620344</v>
+        <v>620311</v>
       </c>
       <c r="R11" t="n">
-        <v>6659640</v>
+        <v>6659658</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,12 +1749,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>mer än 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1787,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023005</v>
+        <v>125044062</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
+        <v>74964</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,25 +1791,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620453</v>
+        <v>620361</v>
       </c>
       <c r="R12" t="n">
-        <v>6659595</v>
+        <v>6659725</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1893,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125024178</v>
+        <v>125044170</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,31 +1897,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1933,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620466</v>
+        <v>620319</v>
       </c>
       <c r="R13" t="n">
-        <v>6659617</v>
+        <v>6659768</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1977,7 +1973,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>cirka 30 bladrosetter</t>
+          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,7 +1982,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2005,10 +2000,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125022973</v>
+        <v>125023498</v>
       </c>
       <c r="B14" t="n">
-        <v>56836</v>
+        <v>57793</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,25 +2012,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,7 +2038,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2053,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620441</v>
+        <v>620453</v>
       </c>
       <c r="R14" t="n">
-        <v>6659571</v>
+        <v>6659605</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2093,7 +2088,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>4 spillningskrokar</t>
+          <t>Sjöng från gran, se bild</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125043140</v>
+        <v>125043295</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
+        <v>95766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2132,25 +2127,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2160,14 +2155,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620353</v>
+        <v>620324</v>
       </c>
       <c r="R15" t="n">
-        <v>6659629</v>
+        <v>6659626</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2227,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023498</v>
+        <v>125022785</v>
       </c>
       <c r="B16" t="n">
-        <v>57793</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,35 +2234,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2275,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620453</v>
+        <v>620445</v>
       </c>
       <c r="R16" t="n">
-        <v>6659605</v>
+        <v>6659540</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2315,7 +2306,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Sjöng från gran, se bild</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,6 +2315,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2564,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125023241</v>
+        <v>125044430</v>
       </c>
       <c r="B19" t="n">
-        <v>56836</v>
+        <v>57793</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,31 +2568,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2608,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620459</v>
+        <v>620191</v>
       </c>
       <c r="R19" t="n">
-        <v>6659598</v>
+        <v>6659731</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2644,11 +2640,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2675,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125043922</v>
+        <v>125022973</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2687,31 +2678,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2719,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620311</v>
+        <v>620441</v>
       </c>
       <c r="R20" t="n">
-        <v>6659658</v>
+        <v>6659571</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2759,7 +2754,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2768,7 +2763,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2787,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125044062</v>
+        <v>125024178</v>
       </c>
       <c r="B21" t="n">
-        <v>74964</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,30 +2793,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2830,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620361</v>
+        <v>620466</v>
       </c>
       <c r="R21" t="n">
-        <v>6659725</v>
+        <v>6659617</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2866,6 +2861,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125043140</v>
+        <v>125044360</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>95766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,14 +1048,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620353</v>
+        <v>620199</v>
       </c>
       <c r="R5" t="n">
-        <v>6659629</v>
+        <v>6659797</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125043766</v>
+        <v>125043140</v>
       </c>
       <c r="B6" t="n">
         <v>98269</v>
@@ -1155,14 +1155,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620301</v>
+        <v>620353</v>
       </c>
       <c r="R6" t="n">
-        <v>6659613</v>
+        <v>6659629</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1195,11 +1195,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125044360</v>
+        <v>125043766</v>
       </c>
       <c r="B7" t="n">
-        <v>95766</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,25 +1234,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620199</v>
+        <v>620301</v>
       </c>
       <c r="R7" t="n">
-        <v>6659797</v>
+        <v>6659613</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1307,6 +1302,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125022785</v>
+        <v>125043872</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
+        <v>57793</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,31 +2234,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2266,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620445</v>
+        <v>620309</v>
       </c>
       <c r="R16" t="n">
-        <v>6659540</v>
+        <v>6659619</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2304,18 +2308,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2334,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125043872</v>
+        <v>125022785</v>
       </c>
       <c r="B17" t="n">
-        <v>57793</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,35 +2344,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2382,10 +2376,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620309</v>
+        <v>620445</v>
       </c>
       <c r="R17" t="n">
-        <v>6659619</v>
+        <v>6659540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2420,12 +2414,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>mer än 30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125023005</v>
+        <v>125044275</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620453</v>
+        <v>620236</v>
       </c>
       <c r="R2" t="n">
-        <v>6659595</v>
+        <v>6659797</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125044275</v>
+        <v>125022785</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620236</v>
+        <v>620445</v>
       </c>
       <c r="R3" t="n">
-        <v>6659797</v>
+        <v>6659540</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Cirka 20 bladrosetter</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125022727</v>
+        <v>125043872</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,7 +922,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -941,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620448</v>
+        <v>620309</v>
       </c>
       <c r="R4" t="n">
-        <v>6659515</v>
+        <v>6659619</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,37 +994,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125044360</v>
+        <v>125043766</v>
       </c>
       <c r="B5" t="n">
-        <v>95766</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620199</v>
+        <v>620301</v>
       </c>
       <c r="R5" t="n">
-        <v>6659797</v>
+        <v>6659613</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,37 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125043140</v>
+        <v>125043295</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,14 +1136,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620353</v>
+        <v>620324</v>
       </c>
       <c r="R6" t="n">
-        <v>6659629</v>
+        <v>6659626</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,15 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125043766</v>
+        <v>125024178</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620301</v>
+        <v>620466</v>
       </c>
       <c r="R7" t="n">
-        <v>6659613</v>
+        <v>6659617</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1306,7 +1282,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,43 +1310,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125023589</v>
+        <v>125044062</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>74983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1378,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620458</v>
+        <v>620361</v>
       </c>
       <c r="R8" t="n">
-        <v>6659607</v>
+        <v>6659725</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1414,11 +1384,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,37 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125043272</v>
+        <v>125022727</v>
       </c>
       <c r="B9" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,7 +1444,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1494,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620344</v>
+        <v>620448</v>
       </c>
       <c r="R9" t="n">
-        <v>6659640</v>
+        <v>6659515</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1530,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,43 +1521,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023241</v>
+        <v>125023005</v>
       </c>
       <c r="B10" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1600,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620459</v>
+        <v>620453</v>
       </c>
       <c r="R10" t="n">
-        <v>6659598</v>
+        <v>6659595</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1638,17 +1597,13 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spillning vid välta</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1667,43 +1622,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125043922</v>
+        <v>125044170</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56842</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1711,10 +1665,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620311</v>
+        <v>620319</v>
       </c>
       <c r="R11" t="n">
-        <v>6659658</v>
+        <v>6659768</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1751,7 +1705,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>mer än 30 bladrosetter</t>
+          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1714,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1779,42 +1732,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125044062</v>
+        <v>125023589</v>
       </c>
       <c r="B12" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1822,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620361</v>
+        <v>620458</v>
       </c>
       <c r="R12" t="n">
-        <v>6659725</v>
+        <v>6659607</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1858,6 +1807,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,37 +1839,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125044170</v>
+        <v>125043272</v>
       </c>
       <c r="B13" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57810</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1923,7 +1872,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1933,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620319</v>
+        <v>620344</v>
       </c>
       <c r="R13" t="n">
-        <v>6659768</v>
+        <v>6659640</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1969,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,47 +1944,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023498</v>
+        <v>125023165</v>
       </c>
       <c r="B14" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2048,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620453</v>
+        <v>620463</v>
       </c>
       <c r="R14" t="n">
-        <v>6659605</v>
+        <v>6659593</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2088,7 +2023,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Sjöng från gran, se bild</t>
+          <t>Flertal plantor på väg i blom</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,6 +2032,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2115,43 +2051,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125043295</v>
+        <v>125023498</v>
       </c>
       <c r="B15" t="n">
-        <v>95766</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57810</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2159,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620324</v>
+        <v>620453</v>
       </c>
       <c r="R15" t="n">
-        <v>6659626</v>
+        <v>6659605</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2197,13 +2132,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sjöng från gran, se bild</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2222,47 +2161,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125043872</v>
+        <v>125023241</v>
       </c>
       <c r="B16" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2270,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620309</v>
+        <v>620459</v>
       </c>
       <c r="R16" t="n">
-        <v>6659619</v>
+        <v>6659598</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2306,6 +2236,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,37 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125022785</v>
+        <v>125044360</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2376,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620445</v>
+        <v>620199</v>
       </c>
       <c r="R17" t="n">
-        <v>6659540</v>
+        <v>6659797</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2412,11 +2342,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,37 +2369,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125023165</v>
+        <v>125043922</v>
       </c>
       <c r="B18" t="n">
-        <v>105293</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98302</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2488,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620463</v>
+        <v>620311</v>
       </c>
       <c r="R18" t="n">
-        <v>6659593</v>
+        <v>6659658</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2528,7 +2448,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flertal plantor på väg i blom</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,37 +2476,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125044430</v>
+        <v>125022973</v>
       </c>
       <c r="B19" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56842</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,7 +2509,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2604,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620191</v>
+        <v>620441</v>
       </c>
       <c r="R19" t="n">
-        <v>6659731</v>
+        <v>6659571</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2640,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,37 +2586,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125022973</v>
+        <v>125044430</v>
       </c>
       <c r="B20" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57810</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,7 +2619,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2714,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620441</v>
+        <v>620191</v>
       </c>
       <c r="R20" t="n">
-        <v>6659571</v>
+        <v>6659731</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2750,11 +2665,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>4 spillningskrokar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,15 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125024178</v>
+        <v>125043140</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,14 +2726,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Svinasjön, norr om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620466</v>
+        <v>620353</v>
       </c>
       <c r="R21" t="n">
-        <v>6659617</v>
+        <v>6659629</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2861,11 +2766,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>cirka 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1842,7 +1842,7 @@
         <v>125043272</v>
       </c>
       <c r="B13" t="n">
-        <v>57810</v>
+        <v>58043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>125023498</v>
       </c>
       <c r="B15" t="n">
-        <v>57810</v>
+        <v>58043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1842,7 +1842,7 @@
         <v>125043272</v>
       </c>
       <c r="B13" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>125023498</v>
       </c>
       <c r="B15" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1842,7 +1842,7 @@
         <v>125043272</v>
       </c>
       <c r="B13" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>125023498</v>
       </c>
       <c r="B15" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1842,7 +1842,7 @@
         <v>125043272</v>
       </c>
       <c r="B13" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>125023498</v>
       </c>
       <c r="B15" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1842,7 +1842,7 @@
         <v>125043272</v>
       </c>
       <c r="B13" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>125023498</v>
       </c>
       <c r="B15" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -1842,7 +1842,7 @@
         <v>125043272</v>
       </c>
       <c r="B13" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>125023498</v>
       </c>
       <c r="B15" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125044275</v>
+        <v>125023005</v>
       </c>
       <c r="B2" t="n">
-        <v>98302</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620236</v>
+        <v>620453</v>
       </c>
       <c r="R2" t="n">
-        <v>6659797</v>
+        <v>6659595</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cirka 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125022785</v>
+        <v>125023743</v>
       </c>
       <c r="B3" t="n">
-        <v>98302</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620445</v>
+        <v>620487</v>
       </c>
       <c r="R3" t="n">
-        <v>6659540</v>
+        <v>6659616</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,11 +851,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,42 +878,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125043872</v>
+        <v>125043295</v>
       </c>
       <c r="B4" t="n">
-        <v>57810</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620309</v>
+        <v>620324</v>
       </c>
       <c r="R4" t="n">
-        <v>6659619</v>
+        <v>6659626</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,6 +961,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125043766</v>
+        <v>125044360</v>
       </c>
       <c r="B5" t="n">
-        <v>98302</v>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620301</v>
+        <v>620199</v>
       </c>
       <c r="R5" t="n">
-        <v>6659613</v>
+        <v>6659797</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1069,11 +1055,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,38 +1082,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125043295</v>
+        <v>125044062</v>
       </c>
       <c r="B6" t="n">
-        <v>95798</v>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1140,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620324</v>
+        <v>620361</v>
       </c>
       <c r="R6" t="n">
-        <v>6659626</v>
+        <v>6659725</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,38 +1183,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125024178</v>
+        <v>125023678</v>
       </c>
       <c r="B7" t="n">
-        <v>98302</v>
+        <v>75300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620466</v>
+        <v>620478</v>
       </c>
       <c r="R7" t="n">
-        <v>6659617</v>
+        <v>6659602</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1282,7 +1261,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>cirka 30 bladrosetter</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125044062</v>
+        <v>125022477</v>
       </c>
       <c r="B8" t="n">
-        <v>74983</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,26 +1300,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1348,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620361</v>
+        <v>620474</v>
       </c>
       <c r="R8" t="n">
-        <v>6659725</v>
+        <v>6659486</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1386,13 +1370,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spillning på nedtrampad häll</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1414,7 +1402,7 @@
         <v>125022727</v>
       </c>
       <c r="B9" t="n">
-        <v>56842</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,37 +1509,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125023005</v>
+        <v>125022973</v>
       </c>
       <c r="B10" t="n">
-        <v>91198</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1559,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620453</v>
+        <v>620441</v>
       </c>
       <c r="R10" t="n">
-        <v>6659595</v>
+        <v>6659571</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1597,13 +1590,17 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4 spillningskrokar</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1622,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125044170</v>
+        <v>125023241</v>
       </c>
       <c r="B11" t="n">
-        <v>56842</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,11 +1650,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1665,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620319</v>
+        <v>620459</v>
       </c>
       <c r="R11" t="n">
-        <v>6659768</v>
+        <v>6659598</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1705,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spillningskrokar på granlåga</t>
+          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,38 +1725,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125023589</v>
+        <v>125044170</v>
       </c>
       <c r="B12" t="n">
-        <v>98302</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1771,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620458</v>
+        <v>620319</v>
       </c>
       <c r="R12" t="n">
-        <v>6659607</v>
+        <v>6659768</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,7 +1808,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>Spillningskrokar på granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,7 +1817,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1839,42 +1835,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125043272</v>
+        <v>125044452</v>
       </c>
       <c r="B13" t="n">
-        <v>58063</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1882,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620344</v>
+        <v>620164</v>
       </c>
       <c r="R13" t="n">
-        <v>6659640</v>
+        <v>6659655</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1918,6 +1910,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning på hällhöjd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125023165</v>
+        <v>122147135</v>
       </c>
       <c r="B14" t="n">
-        <v>105326</v>
+        <v>57132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,38 +1952,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+          <t>Överängen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620463</v>
+        <v>620381</v>
       </c>
       <c r="R14" t="n">
-        <v>6659593</v>
+        <v>6659885</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2013,17 +2015,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flertal plantor på väg i blom</t>
+          <t>Färska spår i snön på bilvägen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2032,19 +2034,18 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Bo Söderström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Bo Söderström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2054,7 +2055,7 @@
         <v>125023498</v>
       </c>
       <c r="B15" t="n">
-        <v>58063</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,38 +2162,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125023241</v>
+        <v>125043272</v>
       </c>
       <c r="B16" t="n">
-        <v>56842</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2200,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620459</v>
+        <v>620344</v>
       </c>
       <c r="R16" t="n">
-        <v>6659598</v>
+        <v>6659640</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2236,11 +2241,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spillning vid välta</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2267,38 +2267,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125044360</v>
+        <v>125043872</v>
       </c>
       <c r="B17" t="n">
-        <v>95798</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2306,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620199</v>
+        <v>620309</v>
       </c>
       <c r="R17" t="n">
-        <v>6659797</v>
+        <v>6659619</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2350,7 +2354,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2369,38 +2372,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125043922</v>
+        <v>125044430</v>
       </c>
       <c r="B18" t="n">
-        <v>98302</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2408,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620311</v>
+        <v>620191</v>
       </c>
       <c r="R18" t="n">
-        <v>6659658</v>
+        <v>6659731</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2446,18 +2453,12 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>mer än 30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2476,42 +2477,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125022973</v>
+        <v>125022785</v>
       </c>
       <c r="B19" t="n">
-        <v>56842</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2519,10 +2516,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620441</v>
+        <v>620445</v>
       </c>
       <c r="R19" t="n">
-        <v>6659571</v>
+        <v>6659540</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2559,7 +2556,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>4 spillningskrokar</t>
+          <t>mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2568,6 +2565,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2586,42 +2584,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125044430</v>
+        <v>125022894</v>
       </c>
       <c r="B20" t="n">
-        <v>57810</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2629,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620191</v>
+        <v>620471</v>
       </c>
       <c r="R20" t="n">
-        <v>6659731</v>
+        <v>6659563</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,12 +2661,18 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125043140</v>
+        <v>125023589</v>
       </c>
       <c r="B21" t="n">
-        <v>98302</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2726,14 +2726,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svinasjön, norr om, Upl</t>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620353</v>
+        <v>620458</v>
       </c>
       <c r="R21" t="n">
-        <v>6659629</v>
+        <v>6659607</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2768,6 +2768,11 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2790,6 +2795,857 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125023832</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>620474</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6659613</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>cirka 20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125024178</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>620466</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6659617</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>cirka 30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125024232</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>620396</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6659633</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>cirka 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125043140</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svinasjön, norr om, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>620353</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6659629</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125043766</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>620301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6659613</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125043922</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>620311</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6659658</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>mer än 30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125044275</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>620236</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6659797</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Cirka 20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125023165</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svinasjön, norr om, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>620463</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6659593</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flertal plantor på väg i blom</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20993-2025 artfynd.xlsx
+++ b/artfynd/A 20993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125023005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125023743</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043295</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044360</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044062</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125023678</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125022477</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125022727</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125022973</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125023241</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1832,6 +1887,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044170</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044452</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2049,6 +2114,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122147135</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2159,6 +2229,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125023498</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2264,6 +2339,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043272</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2369,6 +2449,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043872</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044430</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2581,6 +2671,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125022785</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2688,6 +2783,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125022894</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2795,6 +2895,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125023589</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2902,6 +3007,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125023832</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3009,6 +3119,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125024178</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3116,6 +3231,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125024232</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3218,6 +3338,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043140</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3325,6 +3450,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043766</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3432,6 +3562,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043922</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3539,6 +3674,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044275</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3646,8 +3786,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125023165</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>